--- a/artfynd/A 55286-2023 artfynd.xlsx
+++ b/artfynd/A 55286-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55286-2023 artfynd.xlsx
+++ b/artfynd/A 55286-2023 artfynd.xlsx
@@ -1238,7 +1238,7 @@
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">

--- a/artfynd/A 55286-2023 artfynd.xlsx
+++ b/artfynd/A 55286-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>113192706</v>
+        <v>113209175</v>
       </c>
       <c r="B2" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79521</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,44 +686,35 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2180</v>
+        <v>1639</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Blomskägglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Usnea florida</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
+          <t>(L.) Weber ex F.H.Wigg.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Västrum (Västrum), Sm</t>
+          <t>Västrum, Västrum, Sm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>576149</v>
+        <v>576116</v>
       </c>
       <c r="R2" t="n">
-        <v>6382033</v>
+        <v>6382130</v>
       </c>
       <c r="S2" t="n">
         <v>1</v>
@@ -755,22 +741,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
+          <t>2023-11-12</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
+          <t>2023-11-12</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:18</t>
+          <t>14:37</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,60 +783,56 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>113192901</v>
+        <v>113209727</v>
       </c>
       <c r="B3" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93205</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>2058</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Koppartaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum lundellii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Västrum (Västrum), Sm</t>
+          <t>Västralund, Västralund, Sm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>576142</v>
+        <v>576083</v>
       </c>
       <c r="R3" t="n">
-        <v>6382034</v>
+        <v>6381818</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -877,30 +859,21 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2023-11-12</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-11-11</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>15:40</t>
+          <t>2023-11-12</t>
         </is>
       </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
-        <v>0</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -919,15 +892,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>113193019</v>
+        <v>113192706</v>
       </c>
       <c r="B4" t="n">
-        <v>94429</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -952,18 +920,27 @@
           <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="K4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Västrum (Västrum), Sm</t>
+          <t>Västrum, Västrum, Sm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>576153</v>
+        <v>576149</v>
       </c>
       <c r="R4" t="n">
-        <v>6382049</v>
+        <v>6382033</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -995,7 +972,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1005,7 +982,7 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>15:42</t>
+          <t>13:18</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1032,54 +1009,49 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>113209078</v>
+        <v>113193019</v>
       </c>
       <c r="B5" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96708</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>2180</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Västrum (Västrum), Sm</t>
+          <t>Västrum, Västrum, Sm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>576130</v>
+        <v>576153</v>
       </c>
       <c r="R5" t="n">
-        <v>6382153</v>
+        <v>6382049</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1103,22 +1075,22 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2023-11-11</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2023-11-11</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>15:42</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1145,42 +1117,37 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>113209727</v>
+        <v>113206949</v>
       </c>
       <c r="B6" t="n">
-        <v>91613</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>2058</v>
+        <v>5420</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Koppartaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hydnellum lundellii</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Maas Geest. &amp; Nannf.) E.Larss., K.H.Larss. &amp; Kõljalg</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1189,17 +1156,16 @@
         </is>
       </c>
       <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Västralund (Västralund), Sm</t>
+          <t>Västrum, Västrum, Sm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>576083</v>
+        <v>576103</v>
       </c>
       <c r="R6" t="n">
-        <v>6381818</v>
+        <v>6381961</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1229,18 +1195,27 @@
           <t>2023-11-12</t>
         </is>
       </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-11-12</t>
         </is>
       </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>13:23</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
       <c r="AE6" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF6" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1259,15 +1234,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>113206949</v>
+        <v>113206347</v>
       </c>
       <c r="B7" t="n">
-        <v>90735</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1275,47 +1245,38 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5420</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Västrum (Västrum), Sm</t>
+          <t>Västrum, Västrum, Sm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>576103</v>
+        <v>576115</v>
       </c>
       <c r="R7" t="n">
-        <v>6381961</v>
+        <v>6381903</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1344,7 +1305,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1354,7 +1315,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>12:48</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1381,60 +1342,46 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>113208550</v>
+        <v>113206520</v>
       </c>
       <c r="B8" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>40</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Västrum (Västrum), Sm</t>
+          <t>Västrum, Västrum, Sm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>576199</v>
+        <v>576097</v>
       </c>
       <c r="R8" t="n">
-        <v>6382034</v>
+        <v>6381940</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1466,7 +1413,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1476,7 +1423,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:37</t>
+          <t>13:01</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,15 +1450,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>113209175</v>
+        <v>113209078</v>
       </c>
       <c r="B9" t="n">
-        <v>78707</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1519,38 +1461,38 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1639</v>
+        <v>100049</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blomskägglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Usnea florida</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Weber ex F.H.Wigg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Västrum (Västrum), Sm</t>
+          <t>Västrum, Västrum, Sm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>576116</v>
+        <v>576130</v>
       </c>
       <c r="R9" t="n">
-        <v>6382130</v>
+        <v>6382153</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1616,63 +1558,49 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>113207918</v>
+        <v>113209832</v>
       </c>
       <c r="B10" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Västrum (Västrum), Sm</t>
+          <t>Västralund, Västralund, Sm</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>576147</v>
+        <v>576168</v>
       </c>
       <c r="R10" t="n">
-        <v>6382032</v>
+        <v>6381841</v>
       </c>
       <c r="S10" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1701,7 +1629,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1711,7 +1639,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:10</t>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1738,15 +1666,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>113206907</v>
+        <v>113192901</v>
       </c>
       <c r="B11" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1771,18 +1694,27 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Västrum (Västrum), Sm</t>
+          <t>Västrum, Västrum, Sm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>576091</v>
+        <v>576142</v>
       </c>
       <c r="R11" t="n">
-        <v>6381969</v>
+        <v>6382034</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1809,22 +1741,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2023-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-11-12</t>
+          <t>2023-11-11</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:21</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1851,15 +1783,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>113207816</v>
+        <v>113205363</v>
       </c>
       <c r="B12" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1886,7 +1813,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>95</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1897,14 +1824,14 @@
       <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Västrum (Västrum), Sm</t>
+          <t>Västralund, Västralund, Sm</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>576140</v>
+        <v>576105</v>
       </c>
       <c r="R12" t="n">
-        <v>6382033</v>
+        <v>6381857</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1936,7 +1863,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1946,7 +1873,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:33</t>
+          <t>12:12</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1973,54 +1900,49 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>113206347</v>
+        <v>113206907</v>
       </c>
       <c r="B13" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Västrum (Västrum), Sm</t>
+          <t>Västrum, Västrum, Sm</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>576115</v>
+        <v>576091</v>
       </c>
       <c r="R13" t="n">
-        <v>6381903</v>
+        <v>6381969</v>
       </c>
       <c r="S13" t="n">
-        <v>25</v>
+        <v>1</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2049,7 +1971,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2059,7 +1981,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>12:48</t>
+          <t>13:21</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2086,15 +2008,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>113205363</v>
+        <v>113207162</v>
       </c>
       <c r="B14" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2121,7 +2038,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -2132,14 +2049,14 @@
       <c r="K14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Västralund (Västralund), Sm</t>
+          <t>Västrum, Västrum, Sm</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>576105</v>
+        <v>576082</v>
       </c>
       <c r="R14" t="n">
-        <v>6381857</v>
+        <v>6381993</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2171,7 +2088,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2181,7 +2098,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>12:12</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2211,12 +2128,7 @@
         <v>113207539</v>
       </c>
       <c r="B15" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2254,7 +2166,7 @@
       <c r="K15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Västrum (Västrum), Sm</t>
+          <t>Västrum, Västrum, Sm</t>
         </is>
       </c>
       <c r="Q15" t="n">
@@ -2330,15 +2242,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>113207162</v>
+        <v>113207816</v>
       </c>
       <c r="B16" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2365,7 +2272,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -2376,14 +2283,14 @@
       <c r="K16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Västrum (Västrum), Sm</t>
+          <t>Västrum, Västrum, Sm</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>576082</v>
+        <v>576140</v>
       </c>
       <c r="R16" t="n">
-        <v>6381993</v>
+        <v>6382033</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2452,15 +2359,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>113208041</v>
+        <v>113207918</v>
       </c>
       <c r="B17" t="n">
-        <v>97650</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2487,7 +2389,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -2498,14 +2400,14 @@
       <c r="K17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Västrum (Västrum), Sm</t>
+          <t>Västrum, Västrum, Sm</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>576175</v>
+        <v>576147</v>
       </c>
       <c r="R17" t="n">
-        <v>6382025</v>
+        <v>6382032</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2537,7 +2439,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2547,7 +2449,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:16</t>
+          <t>14:10</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2574,51 +2476,55 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>113206520</v>
+        <v>113208041</v>
       </c>
       <c r="B18" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Västrum (Västrum), Sm</t>
+          <t>Västrum, Västrum, Sm</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>576097</v>
+        <v>576175</v>
       </c>
       <c r="R18" t="n">
-        <v>6381940</v>
+        <v>6382025</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2650,7 +2556,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2660,7 +2566,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:01</t>
+          <t>14:16</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2684,6 +2590,123 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>113208550</v>
+      </c>
+      <c r="B19" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Västrum, Västrum, Sm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>576199</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6382034</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Kalmar</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Västervik</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Småland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Hjorted</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-11-12</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>14:37</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Louise Lundberg</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
